--- a/classmado/spreadsheet_template.xlsx
+++ b/classmado/spreadsheet_template.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -686,6 +686,18 @@
       <c r="B27" s="3" t="inlineStr">
         <is>
           <t>教員が画面の🔁ボタンで「この日だけの時間割変更」を入力すると自動作成されます。固定の時間割シートは変わりません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>行事変更</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>教員がページ上部の✏️で「その日の学校予定・日課」を上書きすると自動作成されます。行を消すと取込内容の表示に戻ります。</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1456,7 +1468,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>※アプリ全体の設定です。キーと値の2列で管理します。「今週の週区分」（A/B）は行事予定を取り込んでいれば自動判定され、この値は使われません（未取込時の手動設定用）。「後期開始日」は後期の時間割に切り替わる日（YYYY-MM-DD）。「教科リスト」は教科係の選択肢で、読点・カンマ区切りで変更できます。「行事取込日時」は取込実行時に自動で記録されます。</t>
+          <t>※アプリ全体の設定です。キーと値の2列で管理します。「今週の週区分」（A/B）は行事予定を取り込んでいれば自動判定され、この値は使われません（未取込時の手動設定用）。「後期開始日」は後期の時間割に切り替わる日（YYYY-MM-DD）。「教科リスト」は教科係の選択肢で、読点・カンマ区切りで変更できます。「非表示ワード」を含む行事の項目は生徒の画面に表示されません（教員には表示されます）。「行事取込日時」は取込実行時に自動で記録されます。</t>
         </is>
       </c>
     </row>
@@ -1505,6 +1517,18 @@
       <c r="B5" s="8" t="inlineStr">
         <is>
           <t>国語、数学、理科、社会、GS、音楽、美術、技術、家庭科</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>非表示ワード</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>素点交換、成績交換、学校評価、通知表、分掌会</t>
         </is>
       </c>
     </row>

--- a/classmado/spreadsheet_template.xlsx
+++ b/classmado/spreadsheet_template.xlsx
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>素点交換、成績交換、学校評価、通知表、分掌会</t>
+          <t>素点交換、成績交換、学校評価、通知票、分掌会</t>
         </is>
       </c>
     </row>

--- a/classmado/spreadsheet_template.xlsx
+++ b/classmado/spreadsheet_template.xlsx
@@ -642,7 +642,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>連絡です。アプリ画面から投稿すると自動でここに追記されます。</t>
+          <t>連絡です。アプリ画面から投稿すると自動でここに追記されます。「表示終了日」を過ぎた連絡は自動で一覧から消えます（基本は投稿日当日限り。継続表示は投稿時に日付を指定）。</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -724,12 +724,13 @@
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>※カテゴリは半角英字で subject（教科）/ duty（係）/ committee（委員会）/ exec（実行委員）/ homeroom（学級・担任）のいずれか。アプリ画面から投稿すると自動でここに追記されます。空でも動作します。</t>
+          <t>※カテゴリは半角英字で subject（教科）/ duty（係）/ committee（委員会）/ exec（実行委員）/ homeroom（学級・担任）のいずれか。「表示終了日」は連絡を表示し続ける最終日（YYYY-MM-DD）。投稿日と同じ日付＝その日限りの表示、先の日付＝その日まで継続表示（アプリの投稿フォームで「今日だけ表示」／「日付を指定」として選べます）。過ぎた連絡は新着連絡・連絡一覧のどちらからも自動的に見えなくなります。空欄の行は無期限表示として扱われます。アプリ画面から投稿すると自動でここに追記されます。空でも動作します。</t>
         </is>
       </c>
     </row>
@@ -779,6 +780,11 @@
           <t>投稿日時</t>
         </is>
       </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>表示終了日</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -826,6 +832,11 @@
           <t>2026-08-10 09:10:00</t>
         </is>
       </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -855,7 +866,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>候補曲の中から歌いたい曲を金曜日までにフォームで回答してください。</t>
+          <t>候補曲の中から歌いたい曲を金曜日までにフォームで回答してください（〆切：8/31）。</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -871,6 +882,11 @@
       <c r="I4" s="7" t="inlineStr">
         <is>
           <t>2026-08-12 19:40:00</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
